--- a/artfynd/A 59757-2025 artfynd.xlsx
+++ b/artfynd/A 59757-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130252341</v>
       </c>
       <c r="B2" t="n">
-        <v>78937</v>
+        <v>78940</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 59757-2025 artfynd.xlsx
+++ b/artfynd/A 59757-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130252341</v>
       </c>
       <c r="B2" t="n">
-        <v>78940</v>
+        <v>78966</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 59757-2025 artfynd.xlsx
+++ b/artfynd/A 59757-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130252341</v>
       </c>
       <c r="B2" t="n">
-        <v>78966</v>
+        <v>78968</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 59757-2025 artfynd.xlsx
+++ b/artfynd/A 59757-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130252341</v>
       </c>
       <c r="B2" t="n">
-        <v>78968</v>
+        <v>79084</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 59757-2025 artfynd.xlsx
+++ b/artfynd/A 59757-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130252341</v>
+        <v>135491905</v>
       </c>
       <c r="B2" t="n">
-        <v>79084</v>
+        <v>79405</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,37 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Västbacka, Dlr</t>
+          <t>Långmyran, Långmyran, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>491208</v>
+        <v>491059</v>
       </c>
       <c r="R2" t="n">
-        <v>6830997</v>
+        <v>6830881</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -740,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>14:53</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>14:53</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,15 +760,2363 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>135491978</v>
+      </c>
+      <c r="B3" t="n">
+        <v>79405</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>185</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Långmyran, Långmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>491069</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6830841</v>
+      </c>
+      <c r="S3" t="n">
+        <v>20</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>135492679</v>
+      </c>
+      <c r="B4" t="n">
+        <v>79405</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>185</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Långmyran, Långmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>491026</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6831212</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>135493052</v>
+      </c>
+      <c r="B5" t="n">
+        <v>79405</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>185</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Långmyran, Långmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>491085</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6831178</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>135492448</v>
+      </c>
+      <c r="B6" t="n">
+        <v>79039</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>353</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Långmyran, Långmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>491166</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6830874</v>
+      </c>
+      <c r="S6" t="n">
+        <v>20</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>135492628</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79039</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>353</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Långmyran, Långmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>491187</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6830891</v>
+      </c>
+      <c r="S7" t="n">
+        <v>20</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>135492566</v>
+      </c>
+      <c r="B8" t="n">
+        <v>91988</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>1204</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Gränsticka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Långmyran, Långmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>491172</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6830894</v>
+      </c>
+      <c r="S8" t="n">
+        <v>20</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>135492664</v>
+      </c>
+      <c r="B9" t="n">
+        <v>80489</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Långmyran, Långmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>491025</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6831209</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>135492002</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Långmyran, Långmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>491121</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6830868</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>135492605</v>
+      </c>
+      <c r="B11" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Långmyran, Långmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>491014</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6831273</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>130252341</v>
+      </c>
+      <c r="B12" t="n">
+        <v>79084</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Västbacka, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>491208</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6830997</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>14:53</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>14:53</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
           <t>Bo karlstens</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX12" t="inlineStr">
         <is>
           <t>Bo karlstens</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>135491876</v>
+      </c>
+      <c r="B13" t="n">
+        <v>79130</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Långmyran, Långmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>491069</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6830883</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>135492556</v>
+      </c>
+      <c r="B14" t="n">
+        <v>79130</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Långmyran, Långmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>491018</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6831274</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>135492135</v>
+      </c>
+      <c r="B15" t="n">
+        <v>79992</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Långmyran, Långmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>491085</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6830845</v>
+      </c>
+      <c r="S15" t="n">
+        <v>20</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>135492213</v>
+      </c>
+      <c r="B16" t="n">
+        <v>79992</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Långmyran, Långmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>491091</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6830815</v>
+      </c>
+      <c r="S16" t="n">
+        <v>20</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>135492460</v>
+      </c>
+      <c r="B17" t="n">
+        <v>79992</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Långmyran, Långmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>491166</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6830874</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>135493138</v>
+      </c>
+      <c r="B18" t="n">
+        <v>79992</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Långmyran, Långmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>491099</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6831105</v>
+      </c>
+      <c r="S18" t="n">
+        <v>20</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>135492643</v>
+      </c>
+      <c r="B19" t="n">
+        <v>80488</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Långmyran, Långmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>491024</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6831209</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>135492262</v>
+      </c>
+      <c r="B20" t="n">
+        <v>78377</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6487</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Blågrå svartspik</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis fennica</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Laurila) Tibell</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Långmyran, Långmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>491096</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6830806</v>
+      </c>
+      <c r="S20" t="n">
+        <v>20</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>135492038</v>
+      </c>
+      <c r="B21" t="n">
+        <v>58596</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>103041</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Bergfink</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Fringilla montifringilla</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Långmyran, Långmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>491137</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6830872</v>
+      </c>
+      <c r="S21" t="n">
+        <v>15</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>135492645</v>
+      </c>
+      <c r="B22" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Långmyran, Långmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>491196</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6830908</v>
+      </c>
+      <c r="S22" t="n">
+        <v>20</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>135492018</v>
+      </c>
+      <c r="B23" t="n">
+        <v>79963</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Långmyran, Långmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>491070</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6830818</v>
+      </c>
+      <c r="S23" t="n">
+        <v>20</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>135492107</v>
+      </c>
+      <c r="B24" t="n">
+        <v>79963</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Långmyran, Långmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>491092</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6830831</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>135492585</v>
+      </c>
+      <c r="B25" t="n">
+        <v>79963</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Långmyran, Långmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>491019</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6831271</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>135492777</v>
+      </c>
+      <c r="B26" t="n">
+        <v>79963</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Långmyran, Långmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>491052</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6831206</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 59757-2025 artfynd.xlsx
+++ b/artfynd/A 59757-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY26"/>
+  <dimension ref="A1:AZ26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135491905</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135491978</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135492679</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135493052</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135492448</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135492628</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135492566</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135492664</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135492002</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135492605</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1749,6 +1804,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130252341</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1846,6 +1906,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135491876</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1943,6 +2008,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135492556</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2040,6 +2110,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135492135</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2137,6 +2212,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135492213</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2234,6 +2314,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135492460</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2331,6 +2416,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135493138</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2428,6 +2518,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135492643</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2525,6 +2620,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135492262</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2632,6 +2732,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135492038</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2729,6 +2834,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135492645</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2826,6 +2936,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135492018</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2923,6 +3038,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135492107</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3020,6 +3140,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135492585</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3117,8 +3242,40 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135492777</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 59757-2025 artfynd.xlsx
+++ b/artfynd/A 59757-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135491905</v>
       </c>
       <c r="B2" t="n">
-        <v>79405</v>
+        <v>79443</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135491978</v>
       </c>
       <c r="B3" t="n">
-        <v>79405</v>
+        <v>79443</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>135492679</v>
       </c>
       <c r="B4" t="n">
-        <v>79405</v>
+        <v>79443</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>135493052</v>
       </c>
       <c r="B5" t="n">
-        <v>79405</v>
+        <v>79443</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>135492448</v>
       </c>
       <c r="B6" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>135492628</v>
       </c>
       <c r="B7" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>135492566</v>
       </c>
       <c r="B8" t="n">
-        <v>91988</v>
+        <v>92030</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>135492664</v>
       </c>
       <c r="B9" t="n">
-        <v>80489</v>
+        <v>80527</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>135492002</v>
       </c>
       <c r="B10" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>135492605</v>
       </c>
       <c r="B11" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1815,7 +1815,7 @@
         <v>135491876</v>
       </c>
       <c r="B13" t="n">
-        <v>79130</v>
+        <v>79168</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1917,7 +1917,7 @@
         <v>135492556</v>
       </c>
       <c r="B14" t="n">
-        <v>79130</v>
+        <v>79168</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2019,7 +2019,7 @@
         <v>135492135</v>
       </c>
       <c r="B15" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
         <v>135492213</v>
       </c>
       <c r="B16" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2223,7 +2223,7 @@
         <v>135492460</v>
       </c>
       <c r="B17" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2325,7 +2325,7 @@
         <v>135493138</v>
       </c>
       <c r="B18" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2427,7 +2427,7 @@
         <v>135492643</v>
       </c>
       <c r="B19" t="n">
-        <v>80488</v>
+        <v>80526</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2529,7 +2529,7 @@
         <v>135492262</v>
       </c>
       <c r="B20" t="n">
-        <v>78377</v>
+        <v>78415</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2631,7 +2631,7 @@
         <v>135492038</v>
       </c>
       <c r="B21" t="n">
-        <v>58596</v>
+        <v>58601</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2743,7 +2743,7 @@
         <v>135492645</v>
       </c>
       <c r="B22" t="n">
-        <v>79131</v>
+        <v>79169</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2845,7 +2845,7 @@
         <v>135492018</v>
       </c>
       <c r="B23" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2947,7 +2947,7 @@
         <v>135492107</v>
       </c>
       <c r="B24" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3049,7 +3049,7 @@
         <v>135492585</v>
       </c>
       <c r="B25" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3151,7 +3151,7 @@
         <v>135492777</v>
       </c>
       <c r="B26" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 59757-2025 artfynd.xlsx
+++ b/artfynd/A 59757-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135491905</v>
       </c>
       <c r="B2" t="n">
-        <v>79443</v>
+        <v>79470</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135491978</v>
       </c>
       <c r="B3" t="n">
-        <v>79443</v>
+        <v>79470</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>135492679</v>
       </c>
       <c r="B4" t="n">
-        <v>79443</v>
+        <v>79470</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>135493052</v>
       </c>
       <c r="B5" t="n">
-        <v>79443</v>
+        <v>79470</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>135492448</v>
       </c>
       <c r="B6" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>135492628</v>
       </c>
       <c r="B7" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>135492566</v>
       </c>
       <c r="B8" t="n">
-        <v>92030</v>
+        <v>92057</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>135492664</v>
       </c>
       <c r="B9" t="n">
-        <v>80527</v>
+        <v>80554</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>135492002</v>
       </c>
       <c r="B10" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>135492605</v>
       </c>
       <c r="B11" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1815,7 +1815,7 @@
         <v>135491876</v>
       </c>
       <c r="B13" t="n">
-        <v>79168</v>
+        <v>79195</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1917,7 +1917,7 @@
         <v>135492556</v>
       </c>
       <c r="B14" t="n">
-        <v>79168</v>
+        <v>79195</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2019,7 +2019,7 @@
         <v>135492135</v>
       </c>
       <c r="B15" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
         <v>135492213</v>
       </c>
       <c r="B16" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2223,7 +2223,7 @@
         <v>135492460</v>
       </c>
       <c r="B17" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2325,7 +2325,7 @@
         <v>135493138</v>
       </c>
       <c r="B18" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2427,7 +2427,7 @@
         <v>135492643</v>
       </c>
       <c r="B19" t="n">
-        <v>80526</v>
+        <v>80553</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2529,7 +2529,7 @@
         <v>135492262</v>
       </c>
       <c r="B20" t="n">
-        <v>78415</v>
+        <v>78442</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2743,7 +2743,7 @@
         <v>135492645</v>
       </c>
       <c r="B22" t="n">
-        <v>79169</v>
+        <v>79196</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2845,7 +2845,7 @@
         <v>135492018</v>
       </c>
       <c r="B23" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2947,7 +2947,7 @@
         <v>135492107</v>
       </c>
       <c r="B24" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3049,7 +3049,7 @@
         <v>135492585</v>
       </c>
       <c r="B25" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3151,7 +3151,7 @@
         <v>135492777</v>
       </c>
       <c r="B26" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 59757-2025 artfynd.xlsx
+++ b/artfynd/A 59757-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:AZ26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130252341</v>
+        <v>135491905</v>
       </c>
       <c r="B2" t="n">
-        <v>79084</v>
+        <v>79473</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Västbacka, Dlr</t>
+          <t>Långmyran, Långmyran, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>491208</v>
+        <v>491059</v>
       </c>
       <c r="R2" t="n">
-        <v>6830997</v>
+        <v>6830881</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>14:53</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-12-21</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>14:53</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,24 +765,2516 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/135491905</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>135491978</v>
+      </c>
+      <c r="B3" t="n">
+        <v>79473</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>185</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Långmyran, Långmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>491069</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6830841</v>
+      </c>
+      <c r="S3" t="n">
+        <v>20</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135491978</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>135492679</v>
+      </c>
+      <c r="B4" t="n">
+        <v>79473</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>185</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Långmyran, Långmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>491026</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6831212</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135492679</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>135493052</v>
+      </c>
+      <c r="B5" t="n">
+        <v>79473</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>185</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Långmyran, Långmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>491085</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6831178</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135493052</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>135492448</v>
+      </c>
+      <c r="B6" t="n">
+        <v>79107</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>353</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Långmyran, Långmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>491166</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6830874</v>
+      </c>
+      <c r="S6" t="n">
+        <v>20</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135492448</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>135492628</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79107</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>353</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Långmyran, Långmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>491187</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6830891</v>
+      </c>
+      <c r="S7" t="n">
+        <v>20</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135492628</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>135492566</v>
+      </c>
+      <c r="B8" t="n">
+        <v>92062</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>1204</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Gränsticka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Långmyran, Långmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>491172</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6830894</v>
+      </c>
+      <c r="S8" t="n">
+        <v>20</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135492566</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>135492664</v>
+      </c>
+      <c r="B9" t="n">
+        <v>80557</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Långmyran, Långmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>491025</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6831209</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135492664</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>135492002</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Långmyran, Långmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>491121</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6830868</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135492002</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>135492605</v>
+      </c>
+      <c r="B11" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Långmyran, Långmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>491014</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6831273</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135492605</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>130252341</v>
+      </c>
+      <c r="B12" t="n">
+        <v>79084</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Västbacka, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>491208</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6830997</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>14:53</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>14:53</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/130252341</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>135491876</v>
+      </c>
+      <c r="B13" t="n">
+        <v>79198</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Långmyran, Långmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>491069</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6830883</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135491876</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>135492556</v>
+      </c>
+      <c r="B14" t="n">
+        <v>79198</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Långmyran, Långmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>491018</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6831274</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135492556</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>135492135</v>
+      </c>
+      <c r="B15" t="n">
+        <v>80060</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Långmyran, Långmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>491085</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6830845</v>
+      </c>
+      <c r="S15" t="n">
+        <v>20</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135492135</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>135492213</v>
+      </c>
+      <c r="B16" t="n">
+        <v>80060</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Långmyran, Långmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>491091</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6830815</v>
+      </c>
+      <c r="S16" t="n">
+        <v>20</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135492213</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>135492460</v>
+      </c>
+      <c r="B17" t="n">
+        <v>80060</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Långmyran, Långmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>491166</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6830874</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135492460</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>135493138</v>
+      </c>
+      <c r="B18" t="n">
+        <v>80060</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Långmyran, Långmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>491099</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6831105</v>
+      </c>
+      <c r="S18" t="n">
+        <v>20</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135493138</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>135492643</v>
+      </c>
+      <c r="B19" t="n">
+        <v>80556</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Långmyran, Långmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>491024</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6831209</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135492643</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>135492262</v>
+      </c>
+      <c r="B20" t="n">
+        <v>78445</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6487</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Blågrå svartspik</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis fennica</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Laurila) Tibell</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Långmyran, Långmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>491096</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6830806</v>
+      </c>
+      <c r="S20" t="n">
+        <v>20</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135492262</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>135492038</v>
+      </c>
+      <c r="B21" t="n">
+        <v>58601</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>103041</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Bergfink</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Fringilla montifringilla</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Långmyran, Långmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>491137</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6830872</v>
+      </c>
+      <c r="S21" t="n">
+        <v>15</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135492038</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>135492645</v>
+      </c>
+      <c r="B22" t="n">
+        <v>79199</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Långmyran, Långmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>491196</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6830908</v>
+      </c>
+      <c r="S22" t="n">
+        <v>20</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135492645</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>135492018</v>
+      </c>
+      <c r="B23" t="n">
+        <v>80031</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Långmyran, Långmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>491070</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6830818</v>
+      </c>
+      <c r="S23" t="n">
+        <v>20</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135492018</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>135492107</v>
+      </c>
+      <c r="B24" t="n">
+        <v>80031</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Långmyran, Långmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>491092</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6830831</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135492107</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>135492585</v>
+      </c>
+      <c r="B25" t="n">
+        <v>80031</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Långmyran, Långmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>491019</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6831271</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135492585</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>135492777</v>
+      </c>
+      <c r="B26" t="n">
+        <v>80031</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Långmyran, Långmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>491052</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6831206</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135492777</t>
         </is>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 59757-2025 artfynd.xlsx
+++ b/artfynd/A 59757-2025 artfynd.xlsx
@@ -1295,7 +1295,7 @@
         <v>135492566</v>
       </c>
       <c r="B8" t="n">
-        <v>92062</v>
+        <v>92064</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
